--- a/accessories/cable-4/cable-4.xlsx
+++ b/accessories/cable-4/cable-4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Battery-Lab-Hardware\accessories\cable-4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c0fa0fe96562a9e/Documents/GitHub/Battery-Lab-Hardware/accessories/cable-4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38DE8FE3-D60F-46F8-9068-7C168D66FBB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{38DE8FE3-D60F-46F8-9068-7C168D66FBB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C97CA6F3-0134-4493-AF01-226F0F178216}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="30615" yWindow="1815" windowWidth="21600" windowHeight="11055" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>

--- a/accessories/cable-4/cable-4.xlsx
+++ b/accessories/cable-4/cable-4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c0fa0fe96562a9e/Documents/GitHub/Battery-Lab-Hardware/accessories/cable-4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{38DE8FE3-D60F-46F8-9068-7C168D66FBB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C97CA6F3-0134-4493-AF01-226F0F178216}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{38DE8FE3-D60F-46F8-9068-7C168D66FBB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6559A8AA-06CE-4DEE-9094-5A85EA7C0448}"/>
   <bookViews>
-    <workbookView xWindow="30615" yWindow="1815" windowWidth="21600" windowHeight="11055" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="31305" yWindow="2505" windowWidth="21600" windowHeight="11055" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="66">
   <si>
     <t>Individual Cost</t>
   </si>
@@ -186,6 +186,54 @@
   </si>
   <si>
     <t>SBS 75 8 AWG main contact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SB50/120 T Handle </t>
+  </si>
+  <si>
+    <t>Connector T Handle For SBS® 50, SBS® 75X Series</t>
+  </si>
+  <si>
+    <t>113899P1</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/anderson-power-products-inc/113899P1/10647423?s=N4IgTCBcDaIIxwMwA4CcqAKcQF0C%2BQA</t>
+  </si>
+  <si>
+    <t>Standard Socket Head Cap Screw: M3x0.50, 20 mm Lg, Low-Profile Std, Black Oxide, Alloy Steel, 50 PK</t>
+  </si>
+  <si>
+    <t>LHS4803020-050P1</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/Standard-Socket-Head-Cap-Screw-6EA45</t>
+  </si>
+  <si>
+    <t>T Handle Hex Nut</t>
+  </si>
+  <si>
+    <t>Hex Nut: Std Hex, M3x0.50 Thread, 5.5 mm Hex Wd, 2.4 mm Hex Ht, Steel, Class 8, Zinc-Plated, 100 PK</t>
+  </si>
+  <si>
+    <t>M01300.030.0001</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/Hex-Nut-Std-Hex-26KR85?searchQuery=M01300.030.0001&amp;searchBar=true&amp;tier=Tier+6&amp;suggestConfigId=6&amp;s_e=false</t>
+  </si>
+  <si>
+    <t>SBS75 Handle Screws Long</t>
+  </si>
+  <si>
+    <t>SBS75 Handle Screws Short</t>
+  </si>
+  <si>
+    <t>Standard Socket Head Cap Screw: M3x0.50, 18 mm Lg, Std, Black Oxide, Alloy Steel, Class 12.9, 100 PK</t>
+  </si>
+  <si>
+    <t>M07000.030.0018</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/Standard-Socket-Head-Cap-Screw-6CE54</t>
   </si>
 </sst>
 </file>
@@ -198,7 +246,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -238,6 +286,12 @@
       <color theme="10"/>
       <name val="Aptos Narrow"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -271,7 +325,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -316,6 +370,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -954,47 +1014,103 @@
       <c r="I10" s="4"/>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
+      <c r="A11" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="2">
+        <v>2</v>
+      </c>
+      <c r="E11" s="8">
+        <v>2.72</v>
+      </c>
+      <c r="F11" s="9">
+        <v>5.44</v>
+      </c>
       <c r="G11" s="5"/>
-      <c r="H11" s="1"/>
+      <c r="H11" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="I11" s="4"/>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
+      <c r="A12" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="2">
+        <v>2</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.37</v>
+      </c>
+      <c r="F12" s="9">
+        <v>0.74</v>
+      </c>
       <c r="G12" s="5"/>
-      <c r="H12" s="1"/>
+      <c r="H12" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="I12" s="4"/>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="3"/>
+      <c r="A13" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="12">
+        <v>2</v>
+      </c>
+      <c r="E13" s="13">
+        <v>0.11</v>
+      </c>
+      <c r="F13" s="9">
+        <v>0.22</v>
+      </c>
+      <c r="G13" s="11"/>
+      <c r="H13" s="18" t="s">
+        <v>65</v>
+      </c>
       <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="9"/>
+      <c r="A14" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D14" s="12">
+        <v>4</v>
+      </c>
+      <c r="E14" s="13">
+        <v>0.04</v>
+      </c>
+      <c r="F14" s="9">
+        <v>0.16</v>
+      </c>
       <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
+      <c r="H14" s="18" t="s">
+        <v>60</v>
+      </c>
       <c r="I14" s="11"/>
       <c r="J14" s="11"/>
     </row>
@@ -1030,7 +1146,7 @@
       </c>
       <c r="F18" s="5">
         <f>SUM(F2:F17)</f>
-        <v>268.34000000000003</v>
+        <v>274.90000000000009</v>
       </c>
     </row>
   </sheetData>
@@ -1047,8 +1163,10 @@
     <hyperlink ref="I4" r:id="rId9" xr:uid="{6767DCFE-C4EA-4F98-917F-25EE5BC81B62}"/>
     <hyperlink ref="H9" r:id="rId10" xr:uid="{7788AAC0-3264-469D-9FE8-88ABE62A1188}"/>
     <hyperlink ref="H10" r:id="rId11" xr:uid="{1563652D-3B5B-4137-B0DA-8740E4BAA28B}"/>
+    <hyperlink ref="H11" r:id="rId12" xr:uid="{A2D1FABC-C24E-4C33-87FC-95C9938AAE71}"/>
+    <hyperlink ref="H14" r:id="rId13" xr:uid="{2E781984-C6DC-456D-B0FC-E0C064584B72}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId12"/>
+  <pageSetup orientation="portrait" r:id="rId14"/>
 </worksheet>
 </file>
--- a/accessories/cable-4/cable-4.xlsx
+++ b/accessories/cable-4/cable-4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c0fa0fe96562a9e/Documents/GitHub/Battery-Lab-Hardware/accessories/cable-4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{38DE8FE3-D60F-46F8-9068-7C168D66FBB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6559A8AA-06CE-4DEE-9094-5A85EA7C0448}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{38DE8FE3-D60F-46F8-9068-7C168D66FBB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1DE2739-1A8B-4D06-AEAC-678BC6C532DC}"/>
   <bookViews>
-    <workbookView xWindow="31305" yWindow="2505" windowWidth="21600" windowHeight="11055" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11055" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="62">
   <si>
     <t>Individual Cost</t>
   </si>
@@ -221,19 +221,7 @@
     <t>https://www.grainger.com/product/Hex-Nut-Std-Hex-26KR85?searchQuery=M01300.030.0001&amp;searchBar=true&amp;tier=Tier+6&amp;suggestConfigId=6&amp;s_e=false</t>
   </si>
   <si>
-    <t>SBS75 Handle Screws Long</t>
-  </si>
-  <si>
-    <t>SBS75 Handle Screws Short</t>
-  </si>
-  <si>
-    <t>Standard Socket Head Cap Screw: M3x0.50, 18 mm Lg, Std, Black Oxide, Alloy Steel, Class 12.9, 100 PK</t>
-  </si>
-  <si>
-    <t>M07000.030.0018</t>
-  </si>
-  <si>
-    <t>https://www.grainger.com/product/Standard-Socket-Head-Cap-Screw-6CE54</t>
+    <t>SBS75 Handle Screws</t>
   </si>
 </sst>
 </file>
@@ -395,6 +383,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1049,13 +1041,13 @@
         <v>55</v>
       </c>
       <c r="D12" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12" s="8">
         <v>0.37</v>
       </c>
       <c r="F12" s="9">
-        <v>0.74</v>
+        <v>1.48</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="3" t="s">
@@ -1064,53 +1056,39 @@
       <c r="I12" s="4"/>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
-        <v>62</v>
+      <c r="A13" s="17" t="s">
+        <v>57</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D13" s="12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E13" s="13">
-        <v>0.11</v>
+        <v>0.04</v>
       </c>
       <c r="F13" s="9">
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="G13" s="11"/>
       <c r="H13" s="18" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" s="12">
-        <v>4</v>
-      </c>
-      <c r="E14" s="13">
-        <v>0.04</v>
-      </c>
-      <c r="F14" s="9">
-        <v>0.16</v>
-      </c>
+      <c r="A14" s="17"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="9"/>
       <c r="G14" s="11"/>
-      <c r="H14" s="18" t="s">
-        <v>60</v>
-      </c>
+      <c r="H14" s="18"/>
       <c r="I14" s="11"/>
       <c r="J14" s="11"/>
     </row>
@@ -1146,7 +1124,7 @@
       </c>
       <c r="F18" s="5">
         <f>SUM(F2:F17)</f>
-        <v>274.90000000000009</v>
+        <v>275.42000000000007</v>
       </c>
     </row>
   </sheetData>
@@ -1164,7 +1142,7 @@
     <hyperlink ref="H9" r:id="rId10" xr:uid="{7788AAC0-3264-469D-9FE8-88ABE62A1188}"/>
     <hyperlink ref="H10" r:id="rId11" xr:uid="{1563652D-3B5B-4137-B0DA-8740E4BAA28B}"/>
     <hyperlink ref="H11" r:id="rId12" xr:uid="{A2D1FABC-C24E-4C33-87FC-95C9938AAE71}"/>
-    <hyperlink ref="H14" r:id="rId13" xr:uid="{2E781984-C6DC-456D-B0FC-E0C064584B72}"/>
+    <hyperlink ref="H13" r:id="rId13" xr:uid="{BC800C73-50FD-4614-AC63-1CB86E190ED6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId14"/>
